--- a/results/Int All Data 0.9/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.9/Linea_fi_explain.xlsx
@@ -1736,7 +1736,7 @@
         <v>0.008496342288605768</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0057556081445109</v>
+        <v>0.0057605197358665</v>
       </c>
       <c r="W3" t="n">
         <v>0.005581739458237815</v>
@@ -1751,7 +1751,7 @@
         <v>0.000810714101417642</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001850899169081668</v>
+        <v>-0.00186145325879143</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.0009183291337236645</v>
@@ -1883,7 +1883,7 @@
         <v>0.0168064183055303</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.001393134549296154</v>
+        <v>0.001399797802948735</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0007817243026566622</v>
@@ -1910,7 +1910,7 @@
         <v>0.001206485980445262</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.007402553630313372</v>
+        <v>0.00739658348105964</v>
       </c>
       <c r="CC3" t="n">
         <v>0.004035420926524452</v>
@@ -1922,7 +1922,7 @@
         <v>0.0001407538790158914</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0002926603798370542</v>
+        <v>-0.0002806758988504298</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4492540649354225</v>
@@ -1979,7 +1979,7 @@
         <v>0.01241645133422041</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.022324282387001</v>
+        <v>0.02231875447102532</v>
       </c>
       <c r="CZ3" t="n">
         <v>0.001169782099463721</v>
@@ -2090,7 +2090,7 @@
         <v>0.001486068397401481</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.001996300811687719</v>
+        <v>0.001986044484896524</v>
       </c>
       <c r="EK3" t="n">
         <v>0.00717822715080052</v>
@@ -2120,7 +2120,7 @@
         <v>-7.000951558273072e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.001907502134069695</v>
+        <v>0.001912413725425294</v>
       </c>
       <c r="EU3" t="n">
         <v>0.01801844084556511</v>
@@ -2132,7 +2132,7 @@
         <v>0.009730540561494725</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.00717822715080052</v>
+        <v>0.007172203054414979</v>
       </c>
       <c r="EY3" t="n">
         <v>-0.0002502808676084278</v>
@@ -2205,7 +2205,7 @@
         <v>0.01141050469373721</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01293342840245877</v>
+        <v>0.01294076837293563</v>
       </c>
       <c r="W4" t="n">
         <v>0.009891662057829872</v>
@@ -2220,7 +2220,7 @@
         <v>0.002264186566483591</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005280252425983126</v>
+        <v>0.005308284703046456</v>
       </c>
       <c r="AB4" t="n">
         <v>0.00315950097729028</v>
@@ -2352,7 +2352,7 @@
         <v>0.02707571215990534</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.008353831455223957</v>
+        <v>0.008359552776731487</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002456321813277003</v>
@@ -2379,7 +2379,7 @@
         <v>0.005474056361892487</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.009246438946374216</v>
+        <v>0.009233385387446908</v>
       </c>
       <c r="CC4" t="n">
         <v>0.006617300778151335</v>
@@ -2391,7 +2391,7 @@
         <v>0.004260704551148318</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.005045445930791002</v>
+        <v>0.005040809165732382</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1056909240687135</v>
@@ -2448,7 +2448,7 @@
         <v>0.02030567691462393</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02419640488486369</v>
+        <v>0.02419531449658294</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.001325847265469341</v>
@@ -2559,7 +2559,7 @@
         <v>0.005257061477734946</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.004225640245788434</v>
+        <v>0.004224530815834782</v>
       </c>
       <c r="EK4" t="n">
         <v>0.02033492398467438</v>
@@ -2589,7 +2589,7 @@
         <v>0.0005394520032751379</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.004090667598852033</v>
+        <v>0.004092804028148394</v>
       </c>
       <c r="EU4" t="n">
         <v>0.04716343871930995</v>
@@ -2601,7 +2601,7 @@
         <v>0.02943472841809915</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.02033492398467438</v>
+        <v>0.02033717659361431</v>
       </c>
       <c r="EY4" t="n">
         <v>0.00354555340432271</v>
@@ -2689,7 +2689,7 @@
         <v>-0.003007915567282271</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01445910290237462</v>
+        <v>-0.01456464379947224</v>
       </c>
       <c r="AB5" t="n">
         <v>-0.009868421052631615</v>
@@ -3539,7 +3539,7 @@
         <v>2.763957987838572e-05</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.00033087454038494</v>
+        <v>0.0003060746459917551</v>
       </c>
       <c r="EY6" t="n">
         <v>-0.0002743501061941905</v>
@@ -3759,7 +3759,7 @@
         <v>0.008474186985408661</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.00231671147203586</v>
+        <v>0.002376412964573171</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.0001083436819044881</v>
@@ -3798,7 +3798,7 @@
         <v>0.001217054213647745</v>
       </c>
       <c r="CF7" t="n">
-        <v>-9.090091710126646e-05</v>
+        <v>-3.119942456394909e-05</v>
       </c>
       <c r="CG7" t="n">
         <v>0.4516562474880449</v>
@@ -4267,7 +4267,7 @@
         <v>0.002500987995657447</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.00107152314123049</v>
+        <v>0.001032276673412588</v>
       </c>
       <c r="CG8" t="n">
         <v>0.507885632080561</v>
@@ -4324,7 +4324,7 @@
         <v>0.02146933308340554</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02994472084024318</v>
+        <v>0.02993090105030399</v>
       </c>
       <c r="CZ8" t="n">
         <v>0.001275734273017654</v>
@@ -4435,7 +4435,7 @@
         <v>0.002668122954299024</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.002635680496501949</v>
+        <v>0.002622318657912959</v>
       </c>
       <c r="EK8" t="n">
         <v>0.001777143307210682</v>
@@ -4724,7 +4724,7 @@
         <v>0.01444776119402981</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.02561194029850744</v>
+        <v>0.02555223880597013</v>
       </c>
       <c r="CC9" t="n">
         <v>0.0133083912346339</v>
